--- a/public/detailed_attendance_template.xlsx
+++ b/public/detailed_attendance_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\grsd-ams\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC74BA0C-7A50-469F-A9F3-B0B0158B7DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FFDD16-603A-4CD2-B05F-45016D9075EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,9 +164,6 @@
     <t>Approved by:</t>
   </si>
   <si>
-    <t>Govinda Khanal</t>
-  </si>
-  <si>
     <t>Arun Baidya</t>
   </si>
   <si>
@@ -186,6 +183,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Director, GrSD</t>
+  </si>
+  <si>
+    <t>Hari Sharma</t>
   </si>
 </sst>
 </file>
@@ -539,6 +539,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -560,29 +581,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -975,54 +975,54 @@
       <c r="S1" s="4"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="55" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="63" t="s">
+      <c r="G2" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="61" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="63" t="s">
+      <c r="O2" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="67" t="s">
+      <c r="P2" s="58"/>
+      <c r="Q2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="61" t="s">
+      <c r="R2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="54" t="s">
+      <c r="S2" s="61" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="58"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="62"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="9" t="s">
         <v>11</v>
       </c>
@@ -1047,16 +1047,16 @@
       <c r="M3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="62"/>
+      <c r="N3" s="56"/>
       <c r="O3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="P3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="55"/>
+      <c r="Q3" s="60"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="62"/>
     </row>
     <row r="4" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
@@ -5478,9 +5478,9 @@
       <c r="D196" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="E196" s="56"/>
-      <c r="F196" s="56"/>
-      <c r="G196" s="56"/>
+      <c r="E196" s="63"/>
+      <c r="F196" s="63"/>
+      <c r="G196" s="63"/>
       <c r="H196" s="46"/>
       <c r="J196" s="51"/>
       <c r="K196" s="51"/>
@@ -5499,51 +5499,46 @@
     <row r="197" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="43"/>
       <c r="B197" s="43" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D197" s="49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E197" s="53"/>
       <c r="F197" s="53"/>
       <c r="G197" s="53"/>
       <c r="H197" s="53"/>
       <c r="I197" s="53"/>
-      <c r="J197" s="66"/>
-      <c r="K197" s="66"/>
-      <c r="L197" s="66"/>
-      <c r="M197" s="66"/>
+      <c r="J197" s="54"/>
+      <c r="K197" s="54"/>
+      <c r="L197" s="54"/>
+      <c r="M197" s="54"/>
       <c r="N197" s="49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S197" s="43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="198" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="43"/>
       <c r="B198" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D198" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="D198" s="49" t="s">
+      <c r="N198" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="N198" s="49" t="s">
+      <c r="S198" s="43" t="s">
         <v>31</v>
-      </c>
-      <c r="S198" s="43" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="199" spans="1:19" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="200" spans="1:19" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="J197:M197"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
     <mergeCell ref="S2:S3"/>
     <mergeCell ref="E196:G196"/>
     <mergeCell ref="A2:A3"/>
@@ -5552,6 +5547,11 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="G2:M2"/>
+    <mergeCell ref="J197:M197"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
   </mergeCells>
   <conditionalFormatting sqref="D132:D133">
     <cfRule type="colorScale" priority="669">
@@ -16810,6 +16810,14 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -16818,16 +16826,42 @@
         <color rgb="FFFF7128"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N54:N66">
+    <cfRule type="colorScale" priority="250">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="249">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="248">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="246">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FFFF7128"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="247">
       <colorScale>
         <cfvo type="min"/>
@@ -16837,84 +16871,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="245">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="246">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="250">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="249">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="248">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55 N58 N60 N62 N64 N66 N45 N41:N42 N47:N53">
-    <cfRule type="colorScale" priority="255">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="254">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="253">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="252">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="251">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -16952,6 +16908,34 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="274">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="275">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FFFF7128"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="279">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="278">
       <colorScale>
         <cfvo type="min"/>
@@ -16960,36 +16944,18 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="274">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="279">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="275">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N56:N58">
+    <cfRule type="colorScale" priority="341">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="340">
       <colorScale>
         <cfvo type="min"/>
@@ -17024,17 +16990,51 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="341">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="342">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FFFF7128"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N58 N55 N60 N62 N64 N66 N45 N41:N42 N47:N53">
+    <cfRule type="colorScale" priority="255">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="251">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="254">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="253">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="252">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -17062,6 +17062,14 @@
         <color rgb="FFFF7128"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="81">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
@@ -17070,12 +17078,14 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="81">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
+    <cfRule type="colorScale" priority="71">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="82">
@@ -17086,18 +17096,16 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="71">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N60">
+    <cfRule type="colorScale" priority="105">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
@@ -17108,6 +17116,30 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="91">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="107">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FFFF7128"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
@@ -17118,40 +17150,16 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="107">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="105">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="91">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
@@ -17162,6 +17170,24 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FFFF7128"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -17170,32 +17196,6 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="102">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="89">
       <colorScale>
         <cfvo type="min"/>
@@ -17206,20 +17206,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N62:N63">
+    <cfRule type="colorScale" priority="85">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF66FFFF"/>
+        <color rgb="FFFFFF00"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="86">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FFFF7128"/>
         <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF66FFFF"/>
-        <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -17278,6 +17278,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N64">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
@@ -17286,6 +17294,16 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
+    <cfRule type="colorScale" priority="73">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="100">
       <colorScale>
         <cfvo type="min"/>
@@ -17304,30 +17322,12 @@
         <color rgb="FFFFFF00"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color rgb="FFFFEF9C"/>
-      </colorScale>
-    </cfRule>
     <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FFFF7128"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="73">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
